--- a/data/trans_bre/P5_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 9,03</t>
+          <t>-9,89; 9,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 9,46</t>
+          <t>-13,43; 9,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 8,81</t>
+          <t>-12,96; 9,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 6,37</t>
+          <t>-4,02; 6,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 32,2</t>
+          <t>-27,56; 34,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 28,73</t>
+          <t>-33,11; 29,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 27,98</t>
+          <t>-30,22; 28,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-50,58; 236,47</t>
+          <t>-55,21; 259,0</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,03; -0,51</t>
+          <t>-18,38; -1,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 9,92</t>
+          <t>-8,75; 9,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 4,59</t>
+          <t>-13,05; 4,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 11,47</t>
+          <t>-0,09; 11,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,81; -1,37</t>
+          <t>-49,95; -5,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 39,24</t>
+          <t>-25,9; 36,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 15,08</t>
+          <t>-33,73; 14,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 152,39</t>
+          <t>-0,53; 138,18</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 13,14</t>
+          <t>-3,99; 13,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 7,76</t>
+          <t>-11,93; 8,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 8,32</t>
+          <t>-11,11; 7,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 41,04</t>
+          <t>-4,39; 39,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 79,09</t>
+          <t>-17,5; 79,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 26,57</t>
+          <t>-31,01; 28,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 25,34</t>
+          <t>-26,79; 24,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 276,01</t>
+          <t>-24,52; 269,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 14,5</t>
+          <t>-2,09; 14,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 11,19</t>
+          <t>-8,79; 10,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 7,14</t>
+          <t>-10,08; 7,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 3,93</t>
+          <t>-14,24; 3,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 71,65</t>
+          <t>-7,25; 72,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 24,74</t>
+          <t>-16,39; 22,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 20,27</t>
+          <t>-22,69; 21,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 12,58</t>
+          <t>-35,67; 12,88</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 4,42</t>
+          <t>-4,46; 4,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,99</t>
+          <t>-5,31; 4,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,74</t>
+          <t>-6,96; 2,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 15,42</t>
+          <t>-0,52; 14,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 17,42</t>
+          <t>-14,53; 17,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 14,08</t>
+          <t>-12,94; 13,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 7,8</t>
+          <t>-17,8; 6,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 94,72</t>
+          <t>-3,43; 93,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 9,33</t>
+          <t>-10,0; 9,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 9,49</t>
+          <t>-13,25; 8,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 9,8</t>
+          <t>-13,52; 8,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 6,72</t>
+          <t>-3,39; 6,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 34,49</t>
+          <t>-27,65; 35,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 29,1</t>
+          <t>-32,05; 25,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 28,73</t>
+          <t>-30,26; 27,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,21; 259,0</t>
+          <t>-51,25; 238,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -1,76</t>
+          <t>-18,84; -1,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 9,27</t>
+          <t>-8,15; 9,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 4,27</t>
+          <t>-13,19; 3,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 11,04</t>
+          <t>-0,24; 11,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,95; -5,72</t>
+          <t>-50,27; -3,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 36,57</t>
+          <t>-24,54; 37,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 14,05</t>
+          <t>-33,95; 11,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 138,18</t>
+          <t>-2,31; 142,13</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 13,54</t>
+          <t>-4,46; 13,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 8,39</t>
+          <t>-12,68; 7,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 7,51</t>
+          <t>-10,67; 8,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 39,34</t>
+          <t>-4,24; 39,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 79,35</t>
+          <t>-19,3; 82,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 28,32</t>
+          <t>-31,68; 25,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 24,25</t>
+          <t>-26,28; 27,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 269,12</t>
+          <t>-23,5; 235,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 14,87</t>
+          <t>-2,04; 14,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 10,48</t>
+          <t>-8,51; 11,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 7,3</t>
+          <t>-10,67; 6,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 3,48</t>
+          <t>-14,71; 2,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 72,25</t>
+          <t>-7,04; 70,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 22,81</t>
+          <t>-15,55; 24,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 21,1</t>
+          <t>-24,42; 18,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 12,88</t>
+          <t>-38,19; 8,62</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 4,56</t>
+          <t>-4,13; 4,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,87</t>
+          <t>-5,29; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 2,36</t>
+          <t>-7,73; 2,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,4</t>
+          <t>-0,59; 14,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 17,81</t>
+          <t>-13,9; 17,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 13,67</t>
+          <t>-12,98; 12,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 6,8</t>
+          <t>-18,99; 6,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 93,96</t>
+          <t>-3,99; 92,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 9,57</t>
+          <t>-11,27; 9,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 8,05</t>
+          <t>-13,85; 9,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 8,77</t>
+          <t>-12,94; 8,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 6,85</t>
+          <t>-3,97; 6,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 35,98</t>
+          <t>-30,11; 32,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 25,06</t>
+          <t>-32,67; 28,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 27,26</t>
+          <t>-30,53; 27,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 238,61</t>
+          <t>-52,56; 236,81</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,84; -1,06</t>
+          <t>-18,03; -0,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 9,76</t>
+          <t>-7,75; 9,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 3,35</t>
+          <t>-12,05; 4,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 11,0</t>
+          <t>0,36; 12,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,27; -3,08</t>
+          <t>-47,81; -1,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 37,79</t>
+          <t>-23,29; 39,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 11,2</t>
+          <t>-31,61; 15,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 142,13</t>
+          <t>-1,11; 157,82</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 13,86</t>
+          <t>-4,22; 13,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 7,8</t>
+          <t>-12,47; 7,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 8,44</t>
+          <t>-10,36; 8,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 39,3</t>
+          <t>-8,11; 7,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 82,0</t>
+          <t>-15,95; 79,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 25,61</t>
+          <t>-31,13; 26,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 27,11</t>
+          <t>-25,23; 25,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 235,85</t>
+          <t>-37,42; 54,23</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,16</t>
+          <t>-6,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-14,67%</t>
+          <t>-17,56%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 14,12</t>
+          <t>-1,75; 14,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 11,05</t>
+          <t>-8,55; 11,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 6,67</t>
+          <t>-10,18; 7,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 2,85</t>
+          <t>-15,02; 2,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 70,36</t>
+          <t>-6,71; 71,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 24,76</t>
+          <t>-15,73; 24,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 18,12</t>
+          <t>-22,69; 20,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,19; 8,62</t>
+          <t>-37,95; 7,34</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,53</t>
+          <t>-4,22; 4,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 4,48</t>
+          <t>-5,4; 4,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,14</t>
+          <t>-7,02; 2,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 14,73</t>
+          <t>-2,68; 4,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 17,33</t>
+          <t>-14,08; 17,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 12,29</t>
+          <t>-12,86; 14,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 6,08</t>
+          <t>-17,94; 7,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 92,1</t>
+          <t>-14,1; 30,7</t>
         </is>
       </c>
     </row>
